--- a/src/test/resources/testData/Userdata.xlsx
+++ b/src/test/resources/testData/Userdata.xlsx
@@ -4,11 +4,11 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="400" yWindow="50" windowWidth="13380" windowHeight="4340"/>
+    <workbookView xWindow="80" yWindow="140" windowWidth="19140" windowHeight="7090" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="LoginTestData" sheetId="1" r:id="rId1"/>
+    <sheet name="CreateJobTestData" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="125725"/>
@@ -16,72 +16,177 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
-  <si>
-    <t>UserID</t>
-  </si>
-  <si>
-    <t>UserName</t>
-  </si>
-  <si>
-    <t>FirstName</t>
-  </si>
-  <si>
-    <t>LastName</t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>Password</t>
-  </si>
-  <si>
-    <t>Phone</t>
-  </si>
-  <si>
-    <t>testuser1</t>
-  </si>
-  <si>
-    <t>John</t>
-  </si>
-  <si>
-    <t>Canedy</t>
-  </si>
-  <si>
-    <t>a@gmail.com</t>
-  </si>
-  <si>
-    <t>test@1</t>
-  </si>
-  <si>
-    <t>testuser2</t>
-  </si>
-  <si>
-    <t>Kim</t>
-  </si>
-  <si>
-    <t>Kom</t>
-  </si>
-  <si>
-    <t>b@gmail.com</t>
-  </si>
-  <si>
-    <t>test@2</t>
-  </si>
-  <si>
-    <t>testuser3</t>
-  </si>
-  <si>
-    <t>Smith</t>
-  </si>
-  <si>
-    <t>Steve</t>
-  </si>
-  <si>
-    <t>c@gmail.com</t>
-  </si>
-  <si>
-    <t>test@3</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="57">
+  <si>
+    <t>username</t>
+  </si>
+  <si>
+    <t>password</t>
+  </si>
+  <si>
+    <t>iamfd</t>
+  </si>
+  <si>
+    <t>iamsup</t>
+  </si>
+  <si>
+    <t>iameng</t>
+  </si>
+  <si>
+    <t>mst_service_location_id</t>
+  </si>
+  <si>
+    <t>mst_platform_id</t>
+  </si>
+  <si>
+    <t>mst_warrenty_status_id</t>
+  </si>
+  <si>
+    <t>mst_oem_id</t>
+  </si>
+  <si>
+    <t>customer__first_name</t>
+  </si>
+  <si>
+    <t>customer__last_name</t>
+  </si>
+  <si>
+    <t>customer__mobile_number</t>
+  </si>
+  <si>
+    <t>customer__mobile_number_alt</t>
+  </si>
+  <si>
+    <t>customer__email_id</t>
+  </si>
+  <si>
+    <t>customer__email_id_alt</t>
+  </si>
+  <si>
+    <t>customer_address__flat_number</t>
+  </si>
+  <si>
+    <t>customer_address__apartment_name</t>
+  </si>
+  <si>
+    <t>customer_address__street_name</t>
+  </si>
+  <si>
+    <t>customer_address__landmark</t>
+  </si>
+  <si>
+    <t>customer_address__area</t>
+  </si>
+  <si>
+    <t>customer_address__pincode</t>
+  </si>
+  <si>
+    <t>customer_address__country</t>
+  </si>
+  <si>
+    <t>customer_address__state</t>
+  </si>
+  <si>
+    <t>customer_product__dop</t>
+  </si>
+  <si>
+    <t>customer_product__serial_number</t>
+  </si>
+  <si>
+    <t>customer_product__imei1</t>
+  </si>
+  <si>
+    <t>customer_product__imei2</t>
+  </si>
+  <si>
+    <t>customer_product__popurl</t>
+  </si>
+  <si>
+    <t>customer_product__product_id</t>
+  </si>
+  <si>
+    <t>customer_product__mst_model_id</t>
+  </si>
+  <si>
+    <t>problems__id</t>
+  </si>
+  <si>
+    <t>problems__remark</t>
+  </si>
+  <si>
+    <t>DB</t>
+  </si>
+  <si>
+    <t>MS</t>
+  </si>
+  <si>
+    <t>Emile_McDermott65@yahoo.com</t>
+  </si>
+  <si>
+    <t>c 304</t>
+  </si>
+  <si>
+    <t>Jupiter</t>
+  </si>
+  <si>
+    <t>MG road</t>
+  </si>
+  <si>
+    <t>Bangur Nagar</t>
+  </si>
+  <si>
+    <t>Goregaon West</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>Maharashtra</t>
+  </si>
+  <si>
+    <t>2025-04-06T18:30:00.000Z</t>
+  </si>
+  <si>
+    <t>Battery Issue</t>
+  </si>
+  <si>
+    <t>DALLU</t>
+  </si>
+  <si>
+    <t>KUMAR</t>
+  </si>
+  <si>
+    <t>VIJAY</t>
+  </si>
+  <si>
+    <t>SINGH</t>
+  </si>
+  <si>
+    <t>ASHOK</t>
+  </si>
+  <si>
+    <t>CHAVAN</t>
+  </si>
+  <si>
+    <t>7897891234</t>
+  </si>
+  <si>
+    <t>89899696585623</t>
+  </si>
+  <si>
+    <t>56099696584511</t>
+  </si>
+  <si>
+    <t>15399696584909</t>
+  </si>
+  <si>
+    <t>23459696582111</t>
+  </si>
+  <si>
+    <t>84569696584511</t>
+  </si>
+  <si>
+    <t>78789696584311</t>
   </si>
 </sst>
 </file>
@@ -105,7 +210,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -113,33 +218,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -434,109 +519,39 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
-  <cols>
-    <col min="1" max="1" width="8.7265625" style="1"/>
-    <col min="2" max="2" width="9.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.7265625" style="1"/>
-    <col min="5" max="5" width="12.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.7265625" style="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="2">
-        <v>1010</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="2">
-        <v>1234567897</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="2">
-        <v>1020</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="2">
-        <v>1234567897</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="2">
-        <v>1030</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G4" s="2">
-        <v>1234567897</v>
+      <c r="B4" t="s">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -546,9 +561,619 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:AA7"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="21.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.26953125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="27.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="29.453125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.08984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="28.90625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="33.1796875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="29.08984375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="26.453125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="22.1796875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="25.1796875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="24.81640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="22.54296875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="22.90625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="30.7265625" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="23" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="24" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="27.6328125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="30.54296875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="16.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:27">
+      <c r="A1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L1" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N1" t="s">
+        <v>18</v>
+      </c>
+      <c r="O1" t="s">
+        <v>19</v>
+      </c>
+      <c r="P1" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>21</v>
+      </c>
+      <c r="R1" t="s">
+        <v>22</v>
+      </c>
+      <c r="S1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T1" t="s">
+        <v>24</v>
+      </c>
+      <c r="U1" t="s">
+        <v>25</v>
+      </c>
+      <c r="V1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W1" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J2" t="s">
+        <v>34</v>
+      </c>
+      <c r="K2" t="s">
+        <v>35</v>
+      </c>
+      <c r="L2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O2" t="s">
+        <v>39</v>
+      </c>
+      <c r="P2">
+        <v>411039</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>40</v>
+      </c>
+      <c r="R2" t="s">
+        <v>41</v>
+      </c>
+      <c r="S2" t="s">
+        <v>42</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="W2" t="s">
+        <v>42</v>
+      </c>
+      <c r="X2">
+        <v>1</v>
+      </c>
+      <c r="Y2">
+        <v>1</v>
+      </c>
+      <c r="Z2">
+        <v>1</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27">
+      <c r="A3">
+        <v>0</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I3" t="s">
+        <v>34</v>
+      </c>
+      <c r="J3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K3" t="s">
+        <v>35</v>
+      </c>
+      <c r="L3" t="s">
+        <v>36</v>
+      </c>
+      <c r="M3" t="s">
+        <v>37</v>
+      </c>
+      <c r="N3" t="s">
+        <v>38</v>
+      </c>
+      <c r="O3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P3">
+        <v>411039</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>40</v>
+      </c>
+      <c r="R3" t="s">
+        <v>41</v>
+      </c>
+      <c r="S3" t="s">
+        <v>42</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="W3" t="s">
+        <v>42</v>
+      </c>
+      <c r="X3">
+        <v>1</v>
+      </c>
+      <c r="Y3">
+        <v>1</v>
+      </c>
+      <c r="Z3">
+        <v>1</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27">
+      <c r="A4">
+        <v>0</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K4" t="s">
+        <v>35</v>
+      </c>
+      <c r="L4" t="s">
+        <v>36</v>
+      </c>
+      <c r="M4" t="s">
+        <v>37</v>
+      </c>
+      <c r="N4" t="s">
+        <v>38</v>
+      </c>
+      <c r="O4" t="s">
+        <v>39</v>
+      </c>
+      <c r="P4">
+        <v>411039</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>40</v>
+      </c>
+      <c r="R4" t="s">
+        <v>41</v>
+      </c>
+      <c r="S4" t="s">
+        <v>42</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="V4" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="W4" t="s">
+        <v>42</v>
+      </c>
+      <c r="X4">
+        <v>1</v>
+      </c>
+      <c r="Y4">
+        <v>1</v>
+      </c>
+      <c r="Z4">
+        <v>1</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27">
+      <c r="A5">
+        <v>0</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" t="s">
+        <v>49</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I5" t="s">
+        <v>34</v>
+      </c>
+      <c r="J5" t="s">
+        <v>34</v>
+      </c>
+      <c r="K5" t="s">
+        <v>35</v>
+      </c>
+      <c r="L5" t="s">
+        <v>36</v>
+      </c>
+      <c r="M5" t="s">
+        <v>37</v>
+      </c>
+      <c r="N5" t="s">
+        <v>38</v>
+      </c>
+      <c r="O5" t="s">
+        <v>39</v>
+      </c>
+      <c r="P5">
+        <v>411039</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>40</v>
+      </c>
+      <c r="R5" t="s">
+        <v>41</v>
+      </c>
+      <c r="S5" t="s">
+        <v>42</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="U5" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="V5" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="W5" t="s">
+        <v>42</v>
+      </c>
+      <c r="X5">
+        <v>1</v>
+      </c>
+      <c r="Y5">
+        <v>1</v>
+      </c>
+      <c r="Z5">
+        <v>1</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27">
+      <c r="A6">
+        <v>0</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6" t="s">
+        <v>49</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I6" t="s">
+        <v>34</v>
+      </c>
+      <c r="J6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K6" t="s">
+        <v>35</v>
+      </c>
+      <c r="L6" t="s">
+        <v>36</v>
+      </c>
+      <c r="M6" t="s">
+        <v>37</v>
+      </c>
+      <c r="N6" t="s">
+        <v>38</v>
+      </c>
+      <c r="O6" t="s">
+        <v>39</v>
+      </c>
+      <c r="P6">
+        <v>411039</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>40</v>
+      </c>
+      <c r="R6" t="s">
+        <v>41</v>
+      </c>
+      <c r="S6" t="s">
+        <v>42</v>
+      </c>
+      <c r="T6" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="U6" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="V6" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="W6" t="s">
+        <v>42</v>
+      </c>
+      <c r="X6">
+        <v>1</v>
+      </c>
+      <c r="Y6">
+        <v>1</v>
+      </c>
+      <c r="Z6">
+        <v>1</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27">
+      <c r="A7">
+        <v>0</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F7" t="s">
+        <v>49</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I7" t="s">
+        <v>34</v>
+      </c>
+      <c r="J7" t="s">
+        <v>34</v>
+      </c>
+      <c r="K7" t="s">
+        <v>35</v>
+      </c>
+      <c r="L7" t="s">
+        <v>36</v>
+      </c>
+      <c r="M7" t="s">
+        <v>37</v>
+      </c>
+      <c r="N7" t="s">
+        <v>38</v>
+      </c>
+      <c r="O7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P7">
+        <v>411039</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>40</v>
+      </c>
+      <c r="R7" t="s">
+        <v>41</v>
+      </c>
+      <c r="S7" t="s">
+        <v>42</v>
+      </c>
+      <c r="T7" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="U7" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="V7" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="W7" t="s">
+        <v>42</v>
+      </c>
+      <c r="X7">
+        <v>1</v>
+      </c>
+      <c r="Y7">
+        <v>1</v>
+      </c>
+      <c r="Z7">
+        <v>1</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
